--- a/ig/DM-OCTOBRE-2024/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
+++ b/ig/DM-OCTOBRE-2024/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20240927120000</t>
+    <t>20241025120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-27T12:00:00+01:00</t>
+    <t>2024-10-25T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -627,12 +627,6 @@
     <t>Test de marche 6 minutes</t>
   </si>
   <si>
-    <t>0149</t>
-  </si>
-  <si>
-    <t>Cystographie pédiatrique</t>
-  </si>
-  <si>
     <t>0150</t>
   </si>
   <si>
@@ -2664,7 +2658,7 @@
     <t>0709</t>
   </si>
   <si>
-    <t>Entéro-IRM</t>
+    <t>Colo-IRM et entéro-IRM</t>
   </si>
   <si>
     <t>0710</t>
@@ -4824,7 +4818,7 @@
     <t>1119</t>
   </si>
   <si>
-    <t>Chirurgie du défilé cervico-thoracique</t>
+    <t>Chirurgie du défilé cervico thoraco brachial</t>
   </si>
   <si>
     <t>1120</t>
@@ -5016,7 +5010,7 @@
     <t>1151</t>
   </si>
   <si>
-    <t>Chirurgie oncologique de l'oesophage ou de la jonction gastro-oesophagienne</t>
+    <t>Chirurgie carcinologique de l'oesophage ou de la jonction gastro-oesophagienne</t>
   </si>
   <si>
     <t>1152</t>
@@ -5103,12 +5097,6 @@
     <t>Chirurgie proctologique</t>
   </si>
   <si>
-    <t>1166</t>
-  </si>
-  <si>
-    <t>Colo-IRM et entéro-IRM</t>
-  </si>
-  <si>
     <t>1167</t>
   </si>
   <si>
@@ -5211,12 +5199,6 @@
     <t>Drainage organes profonds abdominaux</t>
   </si>
   <si>
-    <t>1184</t>
-  </si>
-  <si>
-    <t>Echodoppler artériel / veineux</t>
-  </si>
-  <si>
     <t>1185</t>
   </si>
   <si>
@@ -5778,7 +5760,7 @@
     <t>1279</t>
   </si>
   <si>
-    <t>Télésurveillance des prothèses rythmiques</t>
+    <t>Télésurveillance médicale de l'arythmie cardiaque</t>
   </si>
   <si>
     <t>1280</t>
@@ -6537,24 +6519,12 @@
     <t>Centre labellisé Covid-Long</t>
   </si>
   <si>
-    <t>1410</t>
-  </si>
-  <si>
-    <t>Chirurgie carcinologique de l'oesophage</t>
-  </si>
-  <si>
     <t>1411</t>
   </si>
   <si>
     <t>Chirurgie des déformations thoraciques (pectum excavatum)</t>
   </si>
   <si>
-    <t>1412</t>
-  </si>
-  <si>
-    <t>Chirurgie du syndrome du défilé thoraco brachial</t>
-  </si>
-  <si>
     <t>1413</t>
   </si>
   <si>
@@ -6816,13 +6786,13 @@
     <t>1464</t>
   </si>
   <si>
-    <t>Certificats médicaux pour le sport de haut niveau (SHN)</t>
+    <t>Délivrance de certificats médicaux pour le sport de haut niveau (SHN)</t>
   </si>
   <si>
     <t>1465</t>
   </si>
   <si>
-    <t>Certificats spécifiques pour les sportifs en situation de Handicap</t>
+    <t>Délivrance de certificats spécifiques pour les sportifs en situation de Handicap</t>
   </si>
   <si>
     <t>1466</t>
@@ -6925,6 +6895,36 @@
   </si>
   <si>
     <t>Cryothérapie compressive</t>
+  </si>
+  <si>
+    <t>1483</t>
+  </si>
+  <si>
+    <t>Télésurveillance médicale de l'insuffisance cardiaque</t>
+  </si>
+  <si>
+    <t>1484</t>
+  </si>
+  <si>
+    <t>Télésurveillance médicale de l'insuffisance rénale</t>
+  </si>
+  <si>
+    <t>1485</t>
+  </si>
+  <si>
+    <t>Télésurveillance médicale de l'insuffisance respiratoire</t>
+  </si>
+  <si>
+    <t>1486</t>
+  </si>
+  <si>
+    <t>Télésurveillance médicale du diabète</t>
+  </si>
+  <si>
+    <t>1487</t>
+  </si>
+  <si>
+    <t>Télésurveillance médicale en oncologie</t>
   </si>
   <si>
     <t/>
